--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_atacama.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_atacama.xlsx
@@ -362,42 +362,42 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>E_PRENETA_a</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>E_BASNETA_a</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>E_MEDIANETA_a</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>E_SUPNETA_a</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>E_PREBRUT_a</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>E_PRENETA_a</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>E_BASBRUT_a</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>E_BASNETA_a</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>E_MEDIABRUT_a</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>E_MEDIANETA_a</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>E_SUPBRUT_a</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>E_SUPNETA_a</t>
         </is>
       </c>
     </row>
@@ -408,28 +408,28 @@
         </is>
       </c>
       <c r="B2">
+        <v>55.47526</v>
+      </c>
+      <c r="C2">
+        <v>94.55927</v>
+      </c>
+      <c r="D2">
+        <v>82.21657999999999</v>
+      </c>
+      <c r="E2">
+        <v>39.44101</v>
+      </c>
+      <c r="F2">
         <v>55.63749</v>
       </c>
-      <c r="C2">
-        <v>55.47526</v>
-      </c>
-      <c r="D2">
+      <c r="G2">
         <v>98.91591</v>
       </c>
-      <c r="E2">
-        <v>94.55927</v>
-      </c>
-      <c r="F2">
+      <c r="H2">
         <v>101.7783</v>
       </c>
-      <c r="G2">
-        <v>82.21657999999999</v>
-      </c>
-      <c r="H2">
+      <c r="I2">
         <v>58.90696</v>
-      </c>
-      <c r="I2">
-        <v>39.44101</v>
       </c>
     </row>
     <row r="3">
@@ -439,28 +439,28 @@
         </is>
       </c>
       <c r="B3">
+        <v>69.37984</v>
+      </c>
+      <c r="C3">
+        <v>96.93053</v>
+      </c>
+      <c r="D3">
+        <v>79.30728000000001</v>
+      </c>
+      <c r="E3">
+        <v>37.62376</v>
+      </c>
+      <c r="F3">
         <v>69.63824</v>
       </c>
-      <c r="C3">
-        <v>69.37984</v>
-      </c>
-      <c r="D3">
+      <c r="G3">
         <v>102.3021</v>
       </c>
-      <c r="E3">
-        <v>96.93053</v>
-      </c>
-      <c r="F3">
+      <c r="H3">
         <v>98.40142</v>
       </c>
-      <c r="G3">
-        <v>79.30728000000001</v>
-      </c>
-      <c r="H3">
+      <c r="I3">
         <v>60.91466</v>
-      </c>
-      <c r="I3">
-        <v>37.62376</v>
       </c>
     </row>
     <row r="4">
@@ -470,28 +470,28 @@
         </is>
       </c>
       <c r="B4">
+        <v>62.67606</v>
+      </c>
+      <c r="C4">
+        <v>95.75145999999999</v>
+      </c>
+      <c r="D4">
+        <v>78.14336</v>
+      </c>
+      <c r="E4">
+        <v>25.94249</v>
+      </c>
+      <c r="F4">
         <v>62.83255</v>
       </c>
-      <c r="C4">
-        <v>62.67606</v>
-      </c>
-      <c r="D4">
+      <c r="G4">
         <v>100.0531</v>
       </c>
-      <c r="E4">
-        <v>95.75145999999999</v>
-      </c>
-      <c r="F4">
+      <c r="H4">
         <v>103.5253</v>
       </c>
-      <c r="G4">
-        <v>78.14336</v>
-      </c>
-      <c r="H4">
+      <c r="I4">
         <v>34.56869</v>
-      </c>
-      <c r="I4">
-        <v>25.94249</v>
       </c>
     </row>
     <row r="5">
@@ -501,28 +501,28 @@
         </is>
       </c>
       <c r="B5">
+        <v>61.72727</v>
+      </c>
+      <c r="C5">
+        <v>95.87629</v>
+      </c>
+      <c r="D5">
+        <v>83.60849</v>
+      </c>
+      <c r="E5">
+        <v>34.6401</v>
+      </c>
+      <c r="F5">
         <v>61.81818</v>
       </c>
-      <c r="C5">
-        <v>61.72727</v>
-      </c>
-      <c r="D5">
+      <c r="G5">
         <v>101.8193</v>
       </c>
-      <c r="E5">
-        <v>95.87629</v>
-      </c>
-      <c r="F5">
+      <c r="H5">
         <v>95.04716999999999</v>
       </c>
-      <c r="G5">
-        <v>83.60849</v>
-      </c>
-      <c r="H5">
+      <c r="I5">
         <v>57.84062</v>
-      </c>
-      <c r="I5">
-        <v>34.6401</v>
       </c>
     </row>
     <row r="6">
@@ -532,28 +532,28 @@
         </is>
       </c>
       <c r="B6">
+        <v>59.04762</v>
+      </c>
+      <c r="C6">
+        <v>96.36651000000001</v>
+      </c>
+      <c r="D6">
+        <v>86.51685000000001</v>
+      </c>
+      <c r="E6">
+        <v>41.35802</v>
+      </c>
+      <c r="F6">
         <v>59.1342</v>
       </c>
-      <c r="C6">
-        <v>59.04762</v>
-      </c>
-      <c r="D6">
+      <c r="G6">
         <v>101.4745</v>
       </c>
-      <c r="E6">
-        <v>96.36651000000001</v>
-      </c>
-      <c r="F6">
+      <c r="H6">
         <v>105.2094</v>
       </c>
-      <c r="G6">
-        <v>86.51685000000001</v>
-      </c>
-      <c r="H6">
+      <c r="I6">
         <v>65.9808</v>
-      </c>
-      <c r="I6">
-        <v>41.35802</v>
       </c>
     </row>
     <row r="7">
@@ -563,28 +563,28 @@
         </is>
       </c>
       <c r="B7">
+        <v>63.05579</v>
+      </c>
+      <c r="C7">
+        <v>96.38097999999999</v>
+      </c>
+      <c r="D7">
+        <v>86.86994</v>
+      </c>
+      <c r="E7">
+        <v>39.85012</v>
+      </c>
+      <c r="F7">
         <v>63.42633</v>
       </c>
-      <c r="C7">
-        <v>63.05579</v>
-      </c>
-      <c r="D7">
+      <c r="G7">
         <v>99.87886</v>
       </c>
-      <c r="E7">
-        <v>96.38097999999999</v>
-      </c>
-      <c r="F7">
+      <c r="H7">
         <v>101.9913</v>
       </c>
-      <c r="G7">
-        <v>86.86994</v>
-      </c>
-      <c r="H7">
+      <c r="I7">
         <v>57.0358</v>
-      </c>
-      <c r="I7">
-        <v>39.85012</v>
       </c>
     </row>
     <row r="8">
@@ -597,25 +597,25 @@
         <v>59.33504</v>
       </c>
       <c r="C8">
+        <v>97.31183</v>
+      </c>
+      <c r="D8">
+        <v>87.96992</v>
+      </c>
+      <c r="E8">
+        <v>28.00983</v>
+      </c>
+      <c r="F8">
         <v>59.33504</v>
       </c>
-      <c r="D8">
+      <c r="G8">
         <v>101.7921</v>
       </c>
-      <c r="E8">
-        <v>97.31183</v>
-      </c>
-      <c r="F8">
+      <c r="H8">
         <v>98.87218</v>
       </c>
-      <c r="G8">
-        <v>87.96992</v>
-      </c>
-      <c r="H8">
+      <c r="I8">
         <v>40.54054</v>
-      </c>
-      <c r="I8">
-        <v>28.00983</v>
       </c>
     </row>
     <row r="9">
@@ -625,28 +625,28 @@
         </is>
       </c>
       <c r="B9">
+        <v>66.14664</v>
+      </c>
+      <c r="C9">
+        <v>96.54776</v>
+      </c>
+      <c r="D9">
+        <v>86.5</v>
+      </c>
+      <c r="E9">
+        <v>32.81853</v>
+      </c>
+      <c r="F9">
         <v>66.30265</v>
       </c>
-      <c r="C9">
-        <v>66.14664</v>
-      </c>
-      <c r="D9">
+      <c r="G9">
         <v>99.76985000000001</v>
       </c>
-      <c r="E9">
-        <v>96.54776</v>
-      </c>
-      <c r="F9">
+      <c r="H9">
         <v>105.5</v>
       </c>
-      <c r="G9">
-        <v>86.5</v>
-      </c>
-      <c r="H9">
+      <c r="I9">
         <v>48.64865</v>
-      </c>
-      <c r="I9">
-        <v>32.81853</v>
       </c>
     </row>
     <row r="10">
@@ -659,25 +659,25 @@
         <v>69.76743999999999</v>
       </c>
       <c r="C10">
+        <v>95.83649</v>
+      </c>
+      <c r="D10">
+        <v>84.52381</v>
+      </c>
+      <c r="E10">
+        <v>37.4132</v>
+      </c>
+      <c r="F10">
         <v>69.76743999999999</v>
       </c>
-      <c r="D10">
+      <c r="G10">
         <v>100.1514</v>
       </c>
-      <c r="E10">
-        <v>95.83649</v>
-      </c>
-      <c r="F10">
+      <c r="H10">
         <v>106.8027</v>
       </c>
-      <c r="G10">
-        <v>84.52381</v>
-      </c>
-      <c r="H10">
+      <c r="I10">
         <v>60.67708</v>
-      </c>
-      <c r="I10">
-        <v>37.4132</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_atacama.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_atacama.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 19:35</t>
+    <t xml:space="preserve">2026-08-02 19:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_atacama.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_atacama.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-02 19:38</t>
+    <t xml:space="preserve">2026-08-05 10:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_atacama.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_atacama.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-05 10:30</t>
+    <t xml:space="preserve">2026-08-05 18:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_atacama.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_atacama.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-05 18:10</t>
+    <t xml:space="preserve">2026-08-16 09:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_atacama.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_atacama.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-16 09:42</t>
+    <t xml:space="preserve">2026-08-19 11:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_atacama.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_atacama.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 11:37</t>
+    <t xml:space="preserve">2026-08-28 11:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_atacama.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_atacama.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 11:18</t>
+    <t xml:space="preserve">2026-09-06 17:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
